--- a/TeplosilaWeb/Content/properties/htrv3r.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv3r.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user29\Documents\ТЗ программа подбора TRV, RDT\ТЗ клапаны TRV\25.05.2026 (действ)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22451d98f477d1d3/Рабочий стол/TeploSilaWeb/TeplosilaWeb/Content/properties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42B3DCF-5477-40A0-A524-1DF3E260DEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8DA0AD5-3EDD-4652-9975-329E99726E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -117,12 +120,6 @@
     <t>TSL-3000-60-2A-230-IP67</t>
   </si>
   <si>
-    <t>TW5000-XD220-S.14</t>
-  </si>
-  <si>
-    <t>1 (60); 2 (30)</t>
-  </si>
-  <si>
     <t>TSL-1600-25-2AR-230-IP67</t>
   </si>
   <si>
@@ -178,13 +175,19 @@
   </si>
   <si>
     <t>TSL-3000-60-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-10000-60-3A-230-IP65</t>
+  </si>
+  <si>
+    <t>1,5 (40)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +241,13 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -321,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -349,6 +359,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -360,9 +385,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -663,49 +685,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
+      <c r="A1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
         <v>53</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="20">
         <v>54</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1">
         <v>55</v>
@@ -742,20 +764,20 @@
       <c r="B3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="13"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="18"/>
       <c r="O3" s="15" t="s">
         <v>5</v>
       </c>
@@ -774,7 +796,7 @@
         <v>21</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="W3" s="15" t="s">
         <v>12</v>
@@ -783,20 +805,20 @@
     <row r="4" spans="1:23" s="5" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="13"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="18"/>
       <c r="O4" s="15" t="s">
         <v>6</v>
       </c>
@@ -869,7 +891,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6">
         <v>8</v>
@@ -987,7 +1009,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" s="6">
         <v>8</v>
@@ -1046,7 +1068,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="6">
         <v>8</v>
@@ -1164,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" s="6">
         <v>8</v>
@@ -1223,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" s="6">
         <v>8</v>
@@ -1282,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C13" s="6">
         <v>8</v>
@@ -1341,7 +1363,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="6">
         <v>8</v>
@@ -1400,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1453,7 +1475,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1510,7 +1532,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1563,7 +1585,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1669,7 +1691,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -1722,7 +1744,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -1775,7 +1797,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -1828,7 +1850,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -1881,7 +1903,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -1932,7 +1954,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -2134,56 +2156,58 @@
       </c>
     </row>
     <row r="29" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="12">
         <v>24</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="9">
-        <v>0.75</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>5000</v>
-      </c>
-      <c r="R29" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="S29" s="6" t="s">
+      <c r="B29" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="14">
+        <v>1.65</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="12">
+        <v>10000</v>
+      </c>
+      <c r="R29" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="S29" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="T29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="V29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="W29" s="6">
-        <v>30</v>
+      <c r="T29" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="U29" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="V29" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="W29" s="12">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="C4:N4"/>
@@ -2199,8 +2223,6 @@
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="A3:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/TeplosilaWeb/Content/properties/htrv3r.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv3r.xlsx
@@ -15,19 +15,10 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -2206,11 +2197,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="C4:N4"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="W3:W5"/>
     <mergeCell ref="C2:M2"/>
@@ -2223,6 +2209,11 @@
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="C4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/TeplosilaWeb/Content/properties/htrv3r.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv3r.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22451d98f477d1d3/Рабочий стол/TeploSilaWeb/TeplosilaWeb/Content/properties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8DA0AD5-3EDD-4652-9975-329E99726E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8455D200-7151-43AF-8828-359CA5160101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="47">
   <si>
     <t>Условный диаметр DN, мм</t>
   </si>
@@ -172,6 +181,9 @@
   </si>
   <si>
     <t>1,5 (40)</t>
+  </si>
+  <si>
+    <t>TSL-5000-60-2A-230-IP67</t>
   </si>
 </sst>
 </file>
@@ -322,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -358,9 +370,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -660,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="4" customWidth="1"/>
@@ -676,49 +685,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
         <v>53</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>54</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1">
         <v>55</v>
@@ -749,88 +758,88 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="5" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="15" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="15" t="s">
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15" t="s">
+      <c r="T3" s="14"/>
+      <c r="U3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="V3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="W3" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="5" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="16" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="15" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15" t="s">
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
     </row>
     <row r="5" spans="1:23" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="2">
         <v>15</v>
       </c>
@@ -867,15 +876,15 @@
       <c r="N5" s="2">
         <v>200</v>
       </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
     </row>
     <row r="6" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
@@ -2094,104 +2103,155 @@
       </c>
     </row>
     <row r="28" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A28" s="6">
+      <c r="A28" s="12">
         <v>23</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12">
+        <v>2</v>
+      </c>
+      <c r="M28" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q28" s="12">
+        <v>5000</v>
+      </c>
+      <c r="R28" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S28" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="T28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="U28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="V28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="W28" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="6">
+        <v>24</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6">
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6">
         <v>2.5</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M29" s="6">
         <v>1.5</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N29" s="6">
         <v>1</v>
       </c>
-      <c r="O28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q28" s="6">
+      <c r="O29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="6">
         <v>6000</v>
       </c>
-      <c r="R28" s="7" t="s">
+      <c r="R29" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="S28" s="6" t="s">
+      <c r="S29" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="U28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="V28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="W28" s="6">
+      <c r="T29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="U29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W29" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
-        <v>24</v>
-      </c>
-      <c r="B29" s="11" t="s">
+    <row r="30" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>25</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="14">
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="9">
         <v>1.65</v>
       </c>
-      <c r="O29" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="P29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="12">
+      <c r="O30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q30" s="6">
         <v>10000</v>
       </c>
-      <c r="R29" s="13" t="s">
+      <c r="R30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="S29" s="12" t="s">
+      <c r="S30" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T29" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="U29" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="V29" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="W29" s="12">
+      <c r="T30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W30" s="6">
         <v>150</v>
       </c>
     </row>
